--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_task_target.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_task_target.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_task_target" sheetId="1" r:id="rId1"/>
     <sheet name="任务类型备注表" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_task_target!$C$1:$D$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_task_target!$C$1:$D$210</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="546">
   <si>
     <t>编号</t>
   </si>
@@ -1617,24 +1617,6 @@
   </si>
   <si>
     <t>50020011</t>
-  </si>
-  <si>
-    <t>开启&lt;color=#f0d396&gt;【三转转职任务2】&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>击杀&lt;color=#00FF00&gt;暗黑防御者&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>击杀&lt;color=#00FF00&gt;暗黑咒术师&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>击杀&lt;color=#00FF00&gt;暗黑扫荡者&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>开启&lt;color=#f0d396&gt;【三转转职任务3】&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>击杀&lt;color=#00FF00&gt;暗黑指挥官&lt;/color&gt;</t>
   </si>
   <si>
     <t>type</t>
@@ -3152,7 +3134,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -3310,12 +3292,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3864,7 +3840,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V216"/>
+  <dimension ref="A1:V210"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.2857142857143" style="23" customWidth="1"/>
@@ -12114,7 +12090,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="209" ht="16.5" spans="1:22">
+    <row r="209" ht="16.5" spans="1:13">
       <c r="A209" s="60">
         <v>60666102</v>
       </c>
@@ -12145,7 +12121,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="210" ht="16.5" spans="1:22">
+    <row r="210" ht="16.5" spans="1:13">
       <c r="A210" s="60">
         <v>60666103</v>
       </c>
@@ -12176,223 +12152,8 @@
         <v>229</v>
       </c>
     </row>
-    <row r="211" s="14" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A211" s="60">
-        <v>6066611</v>
-      </c>
-      <c r="B211" s="28" t="s">
-        <v>365</v>
-      </c>
-      <c r="C211" s="61" t="s">
-        <v>389</v>
-      </c>
-      <c r="D211" s="61">
-        <v>5</v>
-      </c>
-      <c r="E211" s="61"/>
-      <c r="F211" s="28"/>
-      <c r="G211" s="28"/>
-      <c r="H211" s="28">
-        <v>1</v>
-      </c>
-      <c r="I211" s="49">
-        <v>0</v>
-      </c>
-      <c r="J211" s="49">
-        <v>1</v>
-      </c>
-      <c r="K211" s="50"/>
-      <c r="L211" s="50"/>
-      <c r="M211" s="51" t="s">
-        <v>229</v>
-      </c>
-      <c r="N211" s="28"/>
-      <c r="O211" s="28">
-        <v>1</v>
-      </c>
-      <c r="P211" s="29"/>
-      <c r="R211" s="29"/>
-      <c r="S211" s="29"/>
-      <c r="T211" s="29"/>
-      <c r="U211" s="29"/>
-      <c r="V211" s="29"/>
-    </row>
-    <row r="212" ht="16.5" spans="1:22">
-      <c r="A212" s="60">
-        <v>6066612</v>
-      </c>
-      <c r="B212" s="28" t="s">
-        <v>365</v>
-      </c>
-      <c r="C212" s="23" t="s">
-        <v>390</v>
-      </c>
-      <c r="D212" s="23">
-        <v>51</v>
-      </c>
-      <c r="E212" s="63">
-        <v>700061</v>
-      </c>
-      <c r="H212" s="64">
-        <v>10</v>
-      </c>
-      <c r="I212" s="49">
-        <v>0</v>
-      </c>
-      <c r="J212" s="49">
-        <v>1</v>
-      </c>
-      <c r="K212" s="50"/>
-      <c r="L212" s="50"/>
-      <c r="M212" s="51"/>
-    </row>
-    <row r="213" s="14" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A213" s="60">
-        <v>60666121</v>
-      </c>
-      <c r="B213" s="28" t="s">
-        <v>365</v>
-      </c>
-      <c r="C213" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="D213" s="23">
-        <v>51</v>
-      </c>
-      <c r="E213" s="63">
-        <v>700062</v>
-      </c>
-      <c r="F213" s="23"/>
-      <c r="G213" s="23"/>
-      <c r="H213" s="64">
-        <v>10</v>
-      </c>
-      <c r="I213" s="49">
-        <v>0</v>
-      </c>
-      <c r="J213" s="49">
-        <v>1</v>
-      </c>
-      <c r="K213" s="50"/>
-      <c r="L213" s="50"/>
-      <c r="M213" s="51"/>
-      <c r="N213" s="23"/>
-      <c r="O213" s="23"/>
-      <c r="P213" s="23"/>
-      <c r="R213" s="23"/>
-      <c r="S213" s="23"/>
-      <c r="T213" s="23"/>
-      <c r="U213" s="23"/>
-      <c r="V213" s="23"/>
-    </row>
-    <row r="214" s="14" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A214" s="60">
-        <v>60666122</v>
-      </c>
-      <c r="B214" s="28" t="s">
-        <v>365</v>
-      </c>
-      <c r="C214" s="23" t="s">
-        <v>392</v>
-      </c>
-      <c r="D214" s="23">
-        <v>51</v>
-      </c>
-      <c r="E214" s="63">
-        <v>700063</v>
-      </c>
-      <c r="F214" s="23"/>
-      <c r="G214" s="23"/>
-      <c r="H214" s="64">
-        <v>10</v>
-      </c>
-      <c r="I214" s="49">
-        <v>0</v>
-      </c>
-      <c r="J214" s="49">
-        <v>1</v>
-      </c>
-      <c r="K214" s="50"/>
-      <c r="L214" s="50"/>
-      <c r="M214" s="51"/>
-      <c r="N214" s="23"/>
-      <c r="O214" s="23"/>
-      <c r="P214" s="23"/>
-      <c r="R214" s="23"/>
-      <c r="S214" s="23"/>
-      <c r="T214" s="23"/>
-      <c r="U214" s="23"/>
-      <c r="V214" s="23"/>
-    </row>
-    <row r="215" s="14" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A215" s="60">
-        <v>6066613</v>
-      </c>
-      <c r="B215" s="28" t="s">
-        <v>365</v>
-      </c>
-      <c r="C215" s="61" t="s">
-        <v>393</v>
-      </c>
-      <c r="D215" s="61">
-        <v>5</v>
-      </c>
-      <c r="E215" s="61"/>
-      <c r="F215" s="28"/>
-      <c r="G215" s="28"/>
-      <c r="H215" s="28">
-        <v>1</v>
-      </c>
-      <c r="I215" s="49">
-        <v>0</v>
-      </c>
-      <c r="J215" s="49">
-        <v>1</v>
-      </c>
-      <c r="K215" s="50"/>
-      <c r="L215" s="50"/>
-      <c r="M215" s="51" t="s">
-        <v>229</v>
-      </c>
-      <c r="N215" s="28"/>
-      <c r="O215" s="28">
-        <v>1</v>
-      </c>
-      <c r="P215" s="29"/>
-      <c r="R215" s="29"/>
-      <c r="S215" s="29"/>
-      <c r="T215" s="29"/>
-      <c r="U215" s="29"/>
-      <c r="V215" s="29"/>
-    </row>
-    <row r="216" ht="16.5" spans="1:22">
-      <c r="A216" s="60">
-        <v>6066614</v>
-      </c>
-      <c r="B216" s="28" t="s">
-        <v>365</v>
-      </c>
-      <c r="C216" s="23" t="s">
-        <v>394</v>
-      </c>
-      <c r="D216" s="23">
-        <v>51</v>
-      </c>
-      <c r="E216" s="63">
-        <v>700060</v>
-      </c>
-      <c r="H216" s="23">
-        <v>1</v>
-      </c>
-      <c r="I216" s="23">
-        <v>0</v>
-      </c>
-      <c r="J216" s="23">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:D216" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:D210" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A5">
@@ -12434,31 +12195,6 @@
   <conditionalFormatting sqref="A207">
     <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A211">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A212">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A213">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A214">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A215">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A216">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E216">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A77:A79">
     <cfRule type="duplicateValues" dxfId="0" priority="45"/>
   </conditionalFormatting>
@@ -12471,20 +12207,13 @@
   <conditionalFormatting sqref="A208:A210">
     <cfRule type="duplicateValues" dxfId="0" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E212:E214">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A115 A117:A196 A217:A1048576">
+  <conditionalFormatting sqref="A1:A115 A117:A196 A211:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A4 A6:A76 A80:A115 A117:A169 A179:A180 A183:A196 A217:A1048576">
+  <conditionalFormatting sqref="A1:A4 A6:A76 A80:A115 A117:A169 A179:A180 A183:A196 A211:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="277"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A76 A80:A115 A117:A169 A179:A180 A183:A196 A217:A1048576">
+  <conditionalFormatting sqref="A1:A76 A80:A115 A117:A169 A179:A180 A183:A196 A211:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="63"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12507,7 +12236,7 @@
   <sheetData>
     <row r="2" s="1" customFormat="1" spans="1:4">
       <c r="A2" s="6" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>41</v>
@@ -12521,634 +12250,634 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C4" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C10" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:4">
       <c r="A21" s="4" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" spans="1:4">
       <c r="A25" s="7" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
     </row>
     <row r="29" s="3" customFormat="1" spans="1:4">
       <c r="A29" s="8" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" spans="1:4">
       <c r="A30" s="4" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="4" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B33"/>
       <c r="C33" s="4" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="4" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="4" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="4" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="4" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="4" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" spans="1:4">
       <c r="A38" s="4" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" spans="1:4">
       <c r="A39" s="4" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" spans="1:4">
       <c r="A40" s="8" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B40" s="8"/>
       <c r="C40" s="8" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" spans="1:4">
       <c r="A41" s="4" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" spans="1:4">
       <c r="A42" s="4" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
     </row>
     <row r="43" s="4" customFormat="1" ht="13.5" spans="1:4">
       <c r="A43" s="4" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" spans="1:4">
       <c r="A44" s="9" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="10" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="C45" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="4" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" spans="1:4">
       <c r="A47" s="11" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="4" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="4" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="10" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="C49" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="10" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
     </row>
     <row r="51" s="5" customFormat="1" spans="1:4">
       <c r="A51" s="12" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
     </row>
     <row r="52" s="5" customFormat="1" spans="1:4">
       <c r="A52" s="12" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="C52" s="12"/>
       <c r="D52" s="12" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
     </row>
     <row r="53" spans="1:4">
